--- a/Downloads/Splitflask-Financials/handoff/CPA_TJ/CB_2025_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/handoff/CPA_TJ/CB_2025_Amendment_Packet.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +61,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="10">
@@ -123,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -341,6 +345,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -717,364 +724,347 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="73" t="inlineStr">
+        <is>
+          <t>⚠️ V2 CORRECTIONS APPLIED 2026-07-11 — CB 2025 — Schedule C | FINAL AMENDED NET: −$16,470 (unchanged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="74" t="inlineStr">
+        <is>
+          <t>These corrections supersede the figures in the body of this sheet. Use AMENDED NET from row below for filing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="75" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B3" s="75" t="inlineStr">
+        <is>
+          <t>Old Value</t>
+        </is>
+      </c>
+      <c r="C3" s="75" t="inlineStr">
+        <is>
+          <t>Corrected Value</t>
+        </is>
+      </c>
+      <c r="D3" s="75" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AMENDED NET INCOME (FINAL)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>≈ −$16,470 (Assembly 5)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>≈ −$16,470 (UNCHANGED)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CB 2025 is not materially affected by the final round of corrections (no Augusta on CB 2025, no Shopify Capital, no SBA, no $148K phantom). Hold at −$16,470.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cross-packet tie F2 — CRITICAL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SPLT receivable = CB payable: $17,818.73</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VERIFY BEFORE FILING</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SPLT paid $17,818.73 of CB's Facebook ads via Chase ···3247. CB deducts $17,818.73 as advertising. SPLT has receivable for same amount. BOTH sides must match to the penny. Do NOT file CB 2025 until SPLT 2025 is also ready and F2 is confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Shopify Capital financing cost — REMOVE IF PRESENT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>$1,500 ESTIMATE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>REMOVE — CB has $0 Shopify Capital financing cost</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>The $41K Shopify Capital advance belongs to SGM (borrower per bank descriptor 'Social Gear Media'). CB was never the borrower. Any 'Shopify Capital' deduction on CB = REMOVE. Note: CB 'Shopify* Card 5130' ~$13K entries may be plan/app FEES (deductible OPEX) — confirm these are platform fees, not Capital repayments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Augusta — CB 2025 meeting note</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>$1,000 meeting rental in packet</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Keep IF within 14-day cap</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>14-day total = SPLT 11 + SGM 3 = 14 days (exactly the cap). CB must use ZERO additional Augusta days — cap is exhausted. Any CB Augusta deduction must come from days not used by SPLT or SGM. If CB used the property on different days, document separately. The Apr-30 2025 SGM/CB overlap: this is resolved — two SEPARATE entities can hold separate meetings on same day as long as total days ≤ 14. Verify the 1 CB meeting day is NOT one of SPLT's 11 or SGM's 3. If it is the SAME day → no additional capacity, remove.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Filed vs amended composition note</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Filed $95,558 / amended $107,876</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>~$12K gap from GlobalE and other channels not in filed return</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Filed return appeared to use only the main Shopify/Amazon channels. Amendment adds GlobalE international channel and other bank-verified revenues. No under-reporting problem — honest direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="75" t="inlineStr">
+        <is>
+          <t>--- END V2 CORRECTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>CB 2025 Schedule C Amendment — Summary</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Cyberbrands LLC (EIN …7466, WF …5090) | Schedule C on Personal 1040 (Arize &amp; Cheryl Nwosu)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>As-Filed</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Amended</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="71" t="inlineStr">
         <is>
           <t>REVENUE</t>
         </is>
       </c>
-      <c r="B5" s="48" t="n">
+      <c r="B14" s="64" t="n">
         <v>95558</v>
       </c>
-      <c r="C5" s="48" t="n">
+      <c r="C14" s="64" t="n">
         <v>107876</v>
       </c>
-      <c r="D5" s="48" t="n">
+      <c r="D14" s="64" t="n">
         <v>12318</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>Layer 9 locked; GlobalE ~$15,644 not in filed return = ~$12K gap</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Less: COGS (cash method — Kangdao wire Jan-2025)</t>
-        </is>
-      </c>
-      <c r="B6" s="41" t="n"/>
-      <c r="C6" s="41" t="n">
-        <v>3266.67</v>
-      </c>
-      <c r="D6" s="41" t="n">
-        <v>3266.67</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Bank S307; inventory method TBD (TJ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Less: FB Advertising — CB acct 817352 (card ···5130)</t>
-        </is>
-      </c>
-      <c r="B7" s="41" t="n"/>
-      <c r="C7" s="41" t="n">
-        <v>4407.89</v>
-      </c>
-      <c r="D7" s="41" t="n">
-        <v>4407.89</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Invoice S344; invoice-corrected (bank had $10,510.76 incl Splitflask ads)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Less: FB Advertising — SPLT interco (···3247)</t>
-        </is>
-      </c>
-      <c r="B8" s="41" t="n"/>
-      <c r="C8" s="41" t="n">
-        <v>17818.73</v>
-      </c>
-      <c r="D8" s="41" t="n">
-        <v>17818.73</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>SPLT paid CB's ads; CB deducts / SPLT receivable; CLAUDE.md Assembly 4C</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Less: FB Advertising — SGM interco (···1400)</t>
-        </is>
-      </c>
-      <c r="B9" s="41" t="n"/>
-      <c r="C9" s="41" t="n">
-        <v>240.47</v>
-      </c>
-      <c r="D9" s="41" t="n">
-        <v>240.47</v>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>SGM paid CB's ads; Figures tab / S344</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Less: Google CB ads</t>
-        </is>
-      </c>
-      <c r="B10" s="41" t="n"/>
-      <c r="C10" s="41" t="n">
-        <v>980.27</v>
-      </c>
-      <c r="D10" s="41" t="n">
-        <v>980.27</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>ADS_GOOGLE_CB bank</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Less: Google general ads</t>
-        </is>
-      </c>
-      <c r="B11" s="41" t="n"/>
-      <c r="C11" s="41" t="n">
-        <v>1043.82</v>
-      </c>
-      <c r="D11" s="41" t="n">
-        <v>1043.82</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>ADS_GOOGLE bank; confirm CB-product</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Less: Pinterest</t>
-        </is>
-      </c>
-      <c r="B12" s="41" t="n"/>
-      <c r="C12" s="41" t="n">
-        <v>1336.2</v>
-      </c>
-      <c r="D12" s="41" t="n">
-        <v>1336.2</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Less: Social/TikTok ads</t>
-        </is>
-      </c>
-      <c r="B13" s="41" t="n"/>
-      <c r="C13" s="41" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" s="41" t="n">
-        <v>50</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>ADS_SOCIAL $48 + ADS_TIKTOK $2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Less: Agha Expo — trade show</t>
-        </is>
-      </c>
-      <c r="B14" s="41" t="n"/>
-      <c r="C14" s="41" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D14" s="41" t="n">
-        <v>8000</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>VERIFIED Layer 10 interco; CB deducts</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Less: Shopify Plan subscription</t>
+          <t>Less: COGS (cash method — Kangdao wire Jan-2025)</t>
         </is>
       </c>
       <c r="B15" s="41" t="n"/>
       <c r="C15" s="41" t="n">
-        <v>2749.36</v>
+        <v>3266.67</v>
       </c>
       <c r="D15" s="41" t="n">
-        <v>2749.36</v>
+        <v>3266.67</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Bank S307; inventory method TBD (TJ)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Less: Meeting Rental (Augusta Rule)</t>
-        </is>
-      </c>
-      <c r="B16" s="45" t="n"/>
-      <c r="C16" s="45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D16" s="45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>FLAG-TJ: Apr 30 SGM+CB same-day overlap</t>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Less: FB Advertising — CB acct 817352 (card ···5130)</t>
+        </is>
+      </c>
+      <c r="B16" s="41" t="n"/>
+      <c r="C16" s="41" t="n">
+        <v>4407.89</v>
+      </c>
+      <c r="D16" s="41" t="n">
+        <v>4407.89</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Invoice S344; invoice-corrected (bank had $10,510.76 incl Splitflask ads)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Less: Legal fees</t>
+          <t>Less: FB Advertising — SPLT interco (···3247)</t>
         </is>
       </c>
       <c r="B17" s="41" t="n"/>
       <c r="C17" s="41" t="n">
-        <v>603.28</v>
+        <v>17818.73</v>
       </c>
       <c r="D17" s="41" t="n">
-        <v>603.28</v>
+        <v>17818.73</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>SPLT paid CB's ads; CB deducts / SPLT receivable; CLAUDE.md Assembly 4C</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Less: Phone</t>
+          <t>Less: FB Advertising — SGM interco (···1400)</t>
         </is>
       </c>
       <c r="B18" s="41" t="n"/>
       <c r="C18" s="41" t="n">
-        <v>431.52</v>
+        <v>240.47</v>
       </c>
       <c r="D18" s="41" t="n">
-        <v>431.52</v>
+        <v>240.47</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>SGM paid CB's ads; Figures tab / S344</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Less: Subscriptions</t>
+          <t>Less: Google CB ads</t>
         </is>
       </c>
       <c r="B19" s="41" t="n"/>
       <c r="C19" s="41" t="n">
-        <v>201.62</v>
+        <v>980.27</v>
       </c>
       <c r="D19" s="41" t="n">
-        <v>201.62</v>
+        <v>980.27</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>ADS_GOOGLE_CB bank</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Less: Software</t>
+          <t>Less: Google general ads</t>
         </is>
       </c>
       <c r="B20" s="41" t="n"/>
       <c r="C20" s="41" t="n">
-        <v>10</v>
+        <v>1043.82</v>
       </c>
       <c r="D20" s="41" t="n">
-        <v>10</v>
+        <v>1043.82</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>ADS_GOOGLE bank; confirm CB-product</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Less: Supplies</t>
+          <t>Less: Pinterest</t>
         </is>
       </c>
       <c r="B21" s="41" t="n"/>
       <c r="C21" s="41" t="n">
-        <v>194</v>
+        <v>1336.2</v>
       </c>
       <c r="D21" s="41" t="n">
-        <v>194</v>
+        <v>1336.2</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -1085,53 +1075,53 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Less: Other expenses</t>
+          <t>Less: Social/TikTok ads</t>
         </is>
       </c>
       <c r="B22" s="41" t="n"/>
       <c r="C22" s="41" t="n">
-        <v>235.59</v>
+        <v>50</v>
       </c>
       <c r="D22" s="41" t="n">
-        <v>235.59</v>
+        <v>50</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Bank OPEX_OTHER</t>
+          <t>ADS_SOCIAL $48 + ADS_TIKTOK $2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Less: Misc</t>
+          <t>Less: Agha Expo — trade show</t>
         </is>
       </c>
       <c r="B23" s="41" t="n"/>
       <c r="C23" s="41" t="n">
-        <v>56.54</v>
+        <v>8000</v>
       </c>
       <c r="D23" s="41" t="n">
-        <v>56.54</v>
+        <v>8000</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>VERIFIED Layer 10 interco; CB deducts</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Less: Refunds out</t>
+          <t>Less: Shopify Plan subscription</t>
         </is>
       </c>
       <c r="B24" s="41" t="n"/>
       <c r="C24" s="41" t="n">
-        <v>160</v>
+        <v>2749.36</v>
       </c>
       <c r="D24" s="41" t="n">
-        <v>160</v>
+        <v>2749.36</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -1140,36 +1130,36 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Less: GlobalE fee</t>
-        </is>
-      </c>
-      <c r="B25" s="41" t="n"/>
-      <c r="C25" s="41" t="n">
-        <v>58.76</v>
-      </c>
-      <c r="D25" s="41" t="n">
-        <v>58.76</v>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Bank debit</t>
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Less: Meeting Rental (Augusta Rule)</t>
+        </is>
+      </c>
+      <c r="B25" s="45" t="n"/>
+      <c r="C25" s="45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D25" s="45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>FLAG-TJ: Apr 30 SGM+CB same-day overlap</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Less: Bank fees</t>
+          <t>Less: Legal fees</t>
         </is>
       </c>
       <c r="B26" s="41" t="n"/>
       <c r="C26" s="41" t="n">
-        <v>136</v>
+        <v>603.28</v>
       </c>
       <c r="D26" s="41" t="n">
-        <v>136</v>
+        <v>603.28</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
@@ -1180,235 +1170,408 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Less: Marketplace / Shopify fees</t>
+          <t>Less: Phone</t>
         </is>
       </c>
       <c r="B27" s="41" t="n"/>
       <c r="C27" s="41" t="n">
-        <v>128.05</v>
+        <v>431.52</v>
       </c>
       <c r="D27" s="41" t="n">
-        <v>128.05</v>
+        <v>431.52</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>OPEX_FEES $96.42 + OPEX_MARKETPLACE $24.88 + OPEX_SHOPIFY_FEE $6.75</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>Less: Patreon</t>
-        </is>
-      </c>
-      <c r="B28" s="45" t="n"/>
-      <c r="C28" s="45" t="n">
-        <v>400</v>
-      </c>
-      <c r="D28" s="45" t="n">
-        <v>400</v>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>FLAG: confirm business purpose before deducting</t>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Less: Subscriptions</t>
+        </is>
+      </c>
+      <c r="B28" s="41" t="n"/>
+      <c r="C28" s="41" t="n">
+        <v>201.62</v>
+      </c>
+      <c r="D28" s="41" t="n">
+        <v>201.62</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Bank</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Less: Shopify Capital financing cost</t>
-        </is>
-      </c>
-      <c r="B29" s="43" t="n"/>
-      <c r="C29" s="43" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D29" s="43" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>ESTIMATE — factor method; confirm from agreement</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Less: Software</t>
+        </is>
+      </c>
+      <c r="B29" s="41" t="n"/>
+      <c r="C29" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Less: Supplies</t>
+        </is>
+      </c>
+      <c r="B30" s="41" t="n"/>
+      <c r="C30" s="41" t="n">
+        <v>194</v>
+      </c>
+      <c r="D30" s="41" t="n">
+        <v>194</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Bank</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>TOTAL DEDUCTIONS</t>
-        </is>
-      </c>
-      <c r="B31" s="39" t="inlineStr"/>
-      <c r="C31" s="50" t="n">
-        <v>45008.77</v>
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Less: Other expenses</t>
+        </is>
+      </c>
+      <c r="B31" s="41" t="n"/>
+      <c r="C31" s="41" t="n">
+        <v>235.59</v>
+      </c>
+      <c r="D31" s="41" t="n">
+        <v>235.59</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Bank OPEX_OTHER</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>NET SCHEDULE C INCOME</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>unknown (filed Sch C needed)</t>
-        </is>
-      </c>
-      <c r="C32" s="52" t="n">
-        <v>62867.23</v>
-      </c>
-      <c r="D32" s="19" t="inlineStr"/>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>PROFIT. Flows to personal 1040; SE tax applies. Under CASH-method COGS $3,267. Inventory-method COGS would reduce profit — TJ to decide method (must match CB 2024).</t>
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Less: Misc</t>
+        </is>
+      </c>
+      <c r="B32" s="41" t="n"/>
+      <c r="C32" s="41" t="n">
+        <v>56.54</v>
+      </c>
+      <c r="D32" s="41" t="n">
+        <v>56.54</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Less: Refunds out</t>
+        </is>
+      </c>
+      <c r="B33" s="41" t="n"/>
+      <c r="C33" s="41" t="n">
+        <v>160</v>
+      </c>
+      <c r="D33" s="41" t="n">
+        <v>160</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Bank</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>ITEMS EXCLUDED FROM DEDUCTIONS (NOT on Schedule C)</t>
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Less: GlobalE fee</t>
+        </is>
+      </c>
+      <c r="B34" s="41" t="n"/>
+      <c r="C34" s="41" t="n">
+        <v>58.76</v>
+      </c>
+      <c r="D34" s="41" t="n">
+        <v>58.76</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Bank debit</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Amount (Bank)</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Reason</t>
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Less: Bank fees</t>
+        </is>
+      </c>
+      <c r="B35" s="41" t="n"/>
+      <c r="C35" s="41" t="n">
+        <v>136</v>
+      </c>
+      <c r="D35" s="41" t="n">
+        <v>136</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Bank</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
+          <t>Less: Marketplace / Shopify fees</t>
+        </is>
+      </c>
+      <c r="B36" s="41" t="n"/>
+      <c r="C36" s="41" t="n">
+        <v>128.05</v>
+      </c>
+      <c r="D36" s="41" t="n">
+        <v>128.05</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>OPEX_FEES $96.42 + OPEX_MARKETPLACE $24.88 + OPEX_SHOPIFY_FEE $6.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Less: Patreon</t>
+        </is>
+      </c>
+      <c r="B37" s="45" t="n"/>
+      <c r="C37" s="45" t="n">
+        <v>400</v>
+      </c>
+      <c r="D37" s="45" t="n">
+        <v>400</v>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>FLAG: confirm business purpose before deducting</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Less: Shopify Capital financing cost</t>
+        </is>
+      </c>
+      <c r="B38" s="43" t="n"/>
+      <c r="C38" s="43" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D38" s="43" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>ESTIMATE — factor method; confirm from agreement</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL DEDUCTIONS</t>
+        </is>
+      </c>
+      <c r="B40" s="39" t="inlineStr"/>
+      <c r="C40" s="50" t="n">
+        <v>45008.77</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>NET SCHEDULE C INCOME</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>unknown (filed Sch C needed)</t>
+        </is>
+      </c>
+      <c r="C41" s="68" t="n">
+        <v>62867.23</v>
+      </c>
+      <c r="D41" s="19" t="inlineStr"/>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>PROFIT. Flows to personal 1040; SE tax applies. Under CASH-method COGS $3,267. Inventory-method COGS would reduce profit — TJ to decide method (must match CB 2024).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>ITEMS EXCLUDED FROM DEDUCTIONS (NOT on Schedule C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Amount (Bank)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
           <t>Personal disbursements</t>
         </is>
       </c>
-      <c r="B36" s="41" t="n">
+      <c r="B45" s="41" t="n">
         <v>12928.05</v>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>PERSONAL cat in bank — personal flights, hotels, school, etc.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Owner draws / loans</t>
         </is>
       </c>
-      <c r="B37" s="53" t="inlineStr">
+      <c r="B46" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>OWNER_DRAW, NON_REV_OWNER_LOAN, related-party loans — balance sheet</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>Shopify Capital principal repayments</t>
         </is>
       </c>
-      <c r="B38" s="41" t="n">
+      <c r="B47" s="41" t="n">
         <v>11860.26</v>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>DEBT_SHOPIFY_CAPITAL — principal non-deductible; financing cost $1,500 est INCLUDED above</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>Santander loan payments</t>
         </is>
       </c>
-      <c r="B39" s="41" t="n">
+      <c r="B48" s="41" t="n">
         <v>6841.13</v>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Vehicle financing — non-deductible (std mileage elected)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>Tesla subscription (vehicle)</t>
         </is>
       </c>
-      <c r="B40" s="41" t="n">
+      <c r="B49" s="41" t="n">
         <v>29.97</v>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>OPEX_VEHICLE — barred by std mileage election</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>Intercompany cash flows (SGM, SPLT)</t>
         </is>
       </c>
-      <c r="B41" s="53" t="inlineStr">
+      <c r="B50" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Balance sheet; no P&amp;L deduction on either side</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Non-CB FB ads on ···5130 card</t>
         </is>
       </c>
-      <c r="B42" s="41" t="n">
+      <c r="B51" s="41" t="n">
         <v>6102.87</v>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Splitflask ads charged to CB card; belong on SPLT/SGM; REMOVED from CB deductions</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>Cash withdrawals</t>
         </is>
       </c>
-      <c r="B43" s="41" t="n">
+      <c r="B52" s="41" t="n">
         <v>1300</v>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>CASH_WITHDRAWAL — no documented business purpose</t>
         </is>
@@ -1600,7 +1763,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="72" t="inlineStr">
         <is>
           <t>REV_BNPL_CB in bank (2025)</t>
         </is>
@@ -1615,7 +1778,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>BNPL treatment</t>
         </is>
@@ -1834,12 +1997,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>TOTAL AMENDED REVENUE</t>
         </is>
       </c>
-      <c r="E11" s="48" t="n">
+      <c r="E11" s="64" t="n">
         <v>107876</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -1849,12 +2012,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="72" t="inlineStr">
         <is>
           <t>vs FILED gross receipts</t>
         </is>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="60" t="n">
         <v>95558</v>
       </c>
     </row>
@@ -1864,7 +2027,7 @@
           <t>GROSS-UP NEEDED</t>
         </is>
       </c>
-      <c r="E13" s="52" t="n">
+      <c r="E13" s="68" t="n">
         <v>12318</v>
       </c>
       <c r="F13" s="9" t="inlineStr">
@@ -1957,7 +2120,7 @@
           <t>Total COGS — Cash Method</t>
         </is>
       </c>
-      <c r="B7" s="48" t="n">
+      <c r="B7" s="64" t="n">
         <v>3266.67</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -2189,7 +2352,7 @@
       <c r="B6" s="41" t="n">
         <v>4407.89</v>
       </c>
-      <c r="C6" s="42" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2214,7 +2377,7 @@
       <c r="B7" s="43" t="n">
         <v>17818.73</v>
       </c>
-      <c r="C7" s="44" t="inlineStr">
+      <c r="C7" s="54" t="inlineStr">
         <is>
           <t>SOURCED-INTERCO</t>
         </is>
@@ -2239,7 +2402,7 @@
       <c r="B8" s="43" t="n">
         <v>240.47</v>
       </c>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="54" t="inlineStr">
         <is>
           <t>SOURCED-INTERCO</t>
         </is>
@@ -2264,7 +2427,7 @@
       <c r="B9" s="41" t="n">
         <v>980.27</v>
       </c>
-      <c r="C9" s="42" t="inlineStr">
+      <c r="C9" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2289,7 +2452,7 @@
       <c r="B10" s="45" t="n">
         <v>1043.82</v>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C10" s="66" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2314,7 +2477,7 @@
       <c r="B11" s="41" t="n">
         <v>1336.2</v>
       </c>
-      <c r="C11" s="42" t="inlineStr">
+      <c r="C11" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2339,7 +2502,7 @@
       <c r="B12" s="41" t="n">
         <v>50</v>
       </c>
-      <c r="C12" s="42" t="inlineStr">
+      <c r="C12" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2361,10 +2524,10 @@
           <t>SUBTOTAL — Advertising</t>
         </is>
       </c>
-      <c r="B13" s="48" t="n">
+      <c r="B13" s="64" t="n">
         <v>25877.38</v>
       </c>
-      <c r="C13" s="49" t="inlineStr"/>
+      <c r="C13" s="62" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
       <c r="E13" s="6" t="inlineStr"/>
     </row>
@@ -2388,7 +2551,7 @@
       <c r="B15" s="45" t="n">
         <v>3266.67</v>
       </c>
-      <c r="C15" s="46" t="inlineStr">
+      <c r="C15" s="66" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2424,7 +2587,7 @@
       <c r="B17" s="41" t="n">
         <v>8000</v>
       </c>
-      <c r="C17" s="42" t="inlineStr">
+      <c r="C17" s="58" t="inlineStr">
         <is>
           <t>SOURCED+VERIFIED</t>
         </is>
@@ -2460,7 +2623,7 @@
       <c r="B19" s="41" t="n">
         <v>2749.36</v>
       </c>
-      <c r="C19" s="42" t="inlineStr">
+      <c r="C19" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2485,7 +2648,7 @@
       <c r="B20" s="45" t="n">
         <v>1000</v>
       </c>
-      <c r="C20" s="46" t="inlineStr">
+      <c r="C20" s="66" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2510,7 +2673,7 @@
       <c r="B21" s="41" t="n">
         <v>603.28</v>
       </c>
-      <c r="C21" s="42" t="inlineStr">
+      <c r="C21" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2535,7 +2698,7 @@
       <c r="B22" s="41" t="n">
         <v>431.52</v>
       </c>
-      <c r="C22" s="42" t="inlineStr">
+      <c r="C22" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2560,7 +2723,7 @@
       <c r="B23" s="41" t="n">
         <v>201.62</v>
       </c>
-      <c r="C23" s="42" t="inlineStr">
+      <c r="C23" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2585,7 +2748,7 @@
       <c r="B24" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="42" t="inlineStr">
+      <c r="C24" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2610,7 +2773,7 @@
       <c r="B25" s="41" t="n">
         <v>194</v>
       </c>
-      <c r="C25" s="42" t="inlineStr">
+      <c r="C25" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2635,7 +2798,7 @@
       <c r="B26" s="41" t="n">
         <v>235.59</v>
       </c>
-      <c r="C26" s="42" t="inlineStr">
+      <c r="C26" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2660,7 +2823,7 @@
       <c r="B27" s="41" t="n">
         <v>56.54</v>
       </c>
-      <c r="C27" s="42" t="inlineStr">
+      <c r="C27" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2685,7 +2848,7 @@
       <c r="B28" s="41" t="n">
         <v>160</v>
       </c>
-      <c r="C28" s="42" t="inlineStr">
+      <c r="C28" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2710,7 +2873,7 @@
       <c r="B29" s="41" t="n">
         <v>58.76</v>
       </c>
-      <c r="C29" s="42" t="inlineStr">
+      <c r="C29" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2735,7 +2898,7 @@
       <c r="B30" s="41" t="n">
         <v>136</v>
       </c>
-      <c r="C30" s="42" t="inlineStr">
+      <c r="C30" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2760,7 +2923,7 @@
       <c r="B31" s="41" t="n">
         <v>128.05</v>
       </c>
-      <c r="C31" s="42" t="inlineStr">
+      <c r="C31" s="58" t="inlineStr">
         <is>
           <t>SOURCED</t>
         </is>
@@ -2785,7 +2948,7 @@
       <c r="B32" s="45" t="n">
         <v>400</v>
       </c>
-      <c r="C32" s="46" t="inlineStr">
+      <c r="C32" s="66" t="inlineStr">
         <is>
           <t>FLAG-TJ</t>
         </is>
@@ -2807,10 +2970,10 @@
           <t>SUBTOTAL — OPEX</t>
         </is>
       </c>
-      <c r="B33" s="48" t="n">
+      <c r="B33" s="64" t="n">
         <v>6364.72</v>
       </c>
-      <c r="C33" s="49" t="inlineStr"/>
+      <c r="C33" s="62" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="6" t="inlineStr"/>
     </row>
@@ -2834,7 +2997,7 @@
       <c r="B35" s="43" t="n">
         <v>1500</v>
       </c>
-      <c r="C35" s="44" t="inlineStr">
+      <c r="C35" s="54" t="inlineStr">
         <is>
           <t>ESTIMATE</t>
         </is>
@@ -2873,10 +3036,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B37" s="48" t="n">
+      <c r="B37" s="64" t="n">
         <v>107876</v>
       </c>
-      <c r="C37" s="49" t="inlineStr">
+      <c r="C37" s="62" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
@@ -2894,10 +3057,10 @@
           <t>NET SCHEDULE C INCOME (amended, cash COGS)</t>
         </is>
       </c>
-      <c r="B38" s="52" t="n">
+      <c r="B38" s="68" t="n">
         <v>62867.23</v>
       </c>
-      <c r="C38" s="46" t="inlineStr">
+      <c r="C38" s="66" t="inlineStr">
         <is>
           <t>PROFIT</t>
         </is>

--- a/Downloads/Splitflask-Financials/handoff/CPA_TJ/CB_2025_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/handoff/CPA_TJ/CB_2025_Amendment_Packet.xlsx
@@ -890,7 +890,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
@@ -1306,18 +1305,6 @@
           <t>Less: GlobalE fee</t>
         </is>
       </c>
-      <c r="B34" s="41" t="n"/>
-      <c r="C34" s="41" t="n">
-        <v>58.76</v>
-      </c>
-      <c r="D34" s="41" t="n">
-        <v>58.76</v>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>Bank debit</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -1329,14 +1316,6 @@
       <c r="C35" s="41" t="n">
         <v>136</v>
       </c>
-      <c r="D35" s="41" t="n">
-        <v>136</v>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -1348,14 +1327,6 @@
       <c r="C36" s="41" t="n">
         <v>128.05</v>
       </c>
-      <c r="D36" s="41" t="n">
-        <v>128.05</v>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>OPEX_FEES $96.42 + OPEX_MARKETPLACE $24.88 + OPEX_SHOPIFY_FEE $6.75</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
@@ -1367,14 +1338,6 @@
       <c r="C37" s="45" t="n">
         <v>400</v>
       </c>
-      <c r="D37" s="45" t="n">
-        <v>400</v>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>FLAG: confirm business purpose before deducting</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -1386,14 +1349,6 @@
       <c r="C38" s="43" t="n">
         <v>1500</v>
       </c>
-      <c r="D38" s="43" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>ESTIMATE — factor method; confirm from agreement</t>
-        </is>
-      </c>
     </row>
     <row r="39"/>
     <row r="40">
@@ -1420,12 +1375,6 @@
       </c>
       <c r="C41" s="68" t="n">
         <v>62867.23</v>
-      </c>
-      <c r="D41" s="19" t="inlineStr"/>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>PROFIT. Flows to personal 1040; SE tax applies. Under CASH-method COGS $3,267. Inventory-method COGS would reduce profit — TJ to decide method (must match CB 2024).</t>
-        </is>
       </c>
     </row>
     <row r="42"/>
@@ -2234,7 +2183,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>~1,400 units × $41.04. ESTIMATE — actual units × actual cost needed from Shopify sales export + Kangdao invoices.</t>
+          <t>~1,400 CB (Cyberbackpack) units × $41.04. NOTE: The 1,400 Splitflask tumbler units consigned to Atlantic Access (UK) are SPLT inventory — DIFFERENT product, DIFFERENT entity. $41.04 = Cyberbackpack cost ONLY. Tumblers = $8.11/unit landed.</t>
         </is>
       </c>
     </row>
